--- a/sheets/대금율보/검수/새타령 (중중모리).xlsx
+++ b/sheets/대금율보/검수/새타령 (중중모리).xlsx
@@ -21954,11 +21954,7 @@
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P17" s="21"/>
       <c r="Q17" s="22"/>
       <c r="R17" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/새타령 (중중모리).xlsx
+++ b/sheets/대금율보/검수/새타령 (중중모리).xlsx
@@ -20629,32 +20629,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -21852,10 +21852,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -21978,7 +21978,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
       </c>
       <c r="U20" s="24"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="22"/>
@@ -22638,7 +22638,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
       </c>
       <c r="U26" s="23"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -22789,7 +22789,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -22868,10 +22868,10 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="80.0" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="119.22" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="119.22" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="23"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="119.22" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="119.22" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="119.22" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -23311,7 +23311,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="119.22" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="119.22" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="119.22" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="24"/>
@@ -23613,7 +23613,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="119.22" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="119.22" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="23"/>
@@ -23775,7 +23775,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="119.22" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
       <c r="T41" s="21"/>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="119.22" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -23907,10 +23907,10 @@
       </c>
       <c r="U42" s="24"/>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="80.0" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="119.22" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="119.22" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="119.22" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
       </c>
       <c r="U47" s="23"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="119.22" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="119.22" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
       <c r="T49" s="21"/>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="119.22" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="119.22" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="119.22" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="119.22" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="22"/>
@@ -24696,7 +24696,7 @@
       <c r="T53" s="21"/>
       <c r="U53" s="22"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="119.22" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="23"/>
@@ -24785,7 +24785,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="119.22" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="23"/>
@@ -24838,7 +24838,7 @@
       <c r="T55" s="21"/>
       <c r="U55" s="23"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="119.22" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -24915,10 +24915,10 @@
       </c>
       <c r="U56" s="24"/>
     </row>
-    <row r="57">
+    <row r="57" ht="6.0" customHeight="true">
       <c r="A57" s="0"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="80.0" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="20" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="119.22" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="119.22" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21"/>
       <c r="C60" s="23"/>
@@ -25106,7 +25106,7 @@
       <c r="T60" s="21"/>
       <c r="U60" s="23"/>
     </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="61" ht="119.22" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="56" customHeight="1">
+    <row r="62" ht="119.22" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21"/>
       <c r="C62" s="24"/>
@@ -25267,7 +25267,7 @@
       </c>
       <c r="U62" s="24"/>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="119.22" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="119.22" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
       </c>
       <c r="U64" s="23"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="119.22" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="119.22" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
       <c r="T66" s="21"/>
       <c r="U66" s="24"/>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="119.22" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21"/>
       <c r="C67" s="22"/>
@@ -25646,7 +25646,7 @@
       <c r="T67" s="21"/>
       <c r="U67" s="22"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="119.22" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
       <c r="T68" s="21"/>
       <c r="U68" s="23"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="119.22" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
       <c r="T69" s="21"/>
       <c r="U69" s="23"/>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="119.22" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21" t="inlineStr">
         <is>
@@ -25854,10 +25854,10 @@
       </c>
       <c r="U70" s="24"/>
     </row>
-    <row r="71">
+    <row r="71" ht="6.0" customHeight="true">
       <c r="A71" s="0"/>
     </row>
-    <row r="72" ht="60" customHeight="1">
+    <row r="72" ht="80.0" customHeight="true">
       <c r="A72" s="0"/>
       <c r="B72" s="20" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
       <c r="T72" s="20"/>
       <c r="U72" s="20"/>
     </row>
-    <row r="73" ht="56" customHeight="1">
+    <row r="73" ht="119.22" customHeight="true">
       <c r="A73" s="0"/>
       <c r="B73" s="21"/>
       <c r="C73" s="22"/>
@@ -25931,7 +25931,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="56" customHeight="1">
+    <row r="74" ht="119.22" customHeight="true">
       <c r="A74" s="0"/>
       <c r="B74" s="21"/>
       <c r="C74" s="23"/>
@@ -25954,7 +25954,7 @@
       <c r="T74" s="21"/>
       <c r="U74" s="23"/>
     </row>
-    <row r="75" ht="56" customHeight="1">
+    <row r="75" ht="119.22" customHeight="true">
       <c r="A75" s="0"/>
       <c r="B75" s="21"/>
       <c r="C75" s="23"/>
@@ -26001,7 +26001,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="56" customHeight="1">
+    <row r="76" ht="119.22" customHeight="true">
       <c r="A76" s="0"/>
       <c r="B76" s="21"/>
       <c r="C76" s="24"/>
@@ -26050,7 +26050,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="56" customHeight="1">
+    <row r="77" ht="119.22" customHeight="true">
       <c r="A77" s="0"/>
       <c r="B77" s="21"/>
       <c r="C77" s="22"/>
@@ -26099,7 +26099,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="56" customHeight="1">
+    <row r="78" ht="119.22" customHeight="true">
       <c r="A78" s="0"/>
       <c r="B78" s="21"/>
       <c r="C78" s="23"/>
@@ -26148,7 +26148,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="56" customHeight="1">
+    <row r="79" ht="119.22" customHeight="true">
       <c r="A79" s="0"/>
       <c r="B79" s="21"/>
       <c r="C79" s="23"/>
@@ -26197,7 +26197,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="56" customHeight="1">
+    <row r="80" ht="119.22" customHeight="true">
       <c r="A80" s="0"/>
       <c r="B80" s="21"/>
       <c r="C80" s="24"/>
@@ -26244,7 +26244,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="56" customHeight="1">
+    <row r="81" ht="119.22" customHeight="true">
       <c r="A81" s="0"/>
       <c r="B81" s="21"/>
       <c r="C81" s="22"/>
@@ -26276,7 +26276,7 @@
       <c r="T81" s="21"/>
       <c r="U81" s="22"/>
     </row>
-    <row r="82" ht="56" customHeight="1">
+    <row r="82" ht="119.22" customHeight="true">
       <c r="A82" s="0"/>
       <c r="B82" s="21"/>
       <c r="C82" s="23"/>
@@ -26320,7 +26320,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="56" customHeight="1">
+    <row r="83" ht="119.22" customHeight="true">
       <c r="A83" s="0"/>
       <c r="B83" s="21"/>
       <c r="C83" s="23"/>
@@ -26351,7 +26351,7 @@
       <c r="T83" s="21"/>
       <c r="U83" s="23"/>
     </row>
-    <row r="84" ht="56" customHeight="1">
+    <row r="84" ht="119.22" customHeight="true">
       <c r="A84" s="0"/>
       <c r="B84" s="21"/>
       <c r="C84" s="24"/>
@@ -26400,7 +26400,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="5" manualBreakCount="5">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
